--- a/spreadsheets/1. initial sizing.xlsx
+++ b/spreadsheets/1. initial sizing.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\KENYA ONE PROJECT\spreadsheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geoff\Google Drive\Kenya One Cranfield Report\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923C948B-C4F7-476F-A268-4792458EA2EF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7160" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Cost Analysis" sheetId="8" r:id="rId1"/>
@@ -27,28 +26,22 @@
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -72,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -96,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D62" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -125,12 +118,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -159,12 +152,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="F5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="A11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -212,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="F18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -238,7 +231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="A21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -262,7 +255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="A22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -276,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+    <comment ref="A24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -300,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J86" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+    <comment ref="J86" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -324,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+    <comment ref="E89" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -348,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+    <comment ref="F89" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -372,7 +365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C98" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+    <comment ref="C98" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -401,12 +394,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="A12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -430,7 +423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="A19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -454,7 +447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="A21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -478,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="A26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -507,12 +500,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="R4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -536,7 +529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+    <comment ref="R5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -560,7 +553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="J6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -584,7 +577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="R6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -608,7 +601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="R7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -632,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
+    <comment ref="R8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -656,7 +649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+    <comment ref="R9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -681,7 +674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+    <comment ref="R10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -705,7 +698,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
+    <comment ref="R11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -729,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
+    <comment ref="R12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -753,7 +746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000B000000}">
+    <comment ref="I13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000C000000}">
+    <comment ref="R13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -801,7 +794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000D000000}">
+    <comment ref="R14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -825,7 +818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
+    <comment ref="R15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -849,7 +842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000F000000}">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -874,7 +867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000010000000}">
+    <comment ref="R17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -899,7 +892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000011000000}">
+    <comment ref="R18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -923,7 +916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000012000000}">
+    <comment ref="R19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -947,7 +940,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000013000000}">
+    <comment ref="R20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -976,12 +969,12 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1006,7 +999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
+    <comment ref="A6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1030,7 +1023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
+    <comment ref="E39" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1045,7 +1038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
+    <comment ref="E44" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1074,12 +1067,12 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1103,7 +1096,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
+    <comment ref="A16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1127,7 +1120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
+    <comment ref="E16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1151,7 +1144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
+    <comment ref="K16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1175,7 +1168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
+    <comment ref="E17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1199,7 +1192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
+    <comment ref="E18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1224,7 +1217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
+    <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1248,7 +1241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000008000000}">
+    <comment ref="G27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1272,7 +1265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000009000000}">
+    <comment ref="A29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1297,7 +1290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000A000000}">
+    <comment ref="G29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1321,7 +1314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000B000000}">
+    <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1345,7 +1338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000C000000}">
+    <comment ref="A31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1369,7 +1362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000D000000}">
+    <comment ref="A33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1393,7 +1386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000E000000}">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1422,12 +1415,12 @@
 </file>
 
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1451,7 +1444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
+    <comment ref="E6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1475,7 +1468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
+    <comment ref="E7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1499,7 +1492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
+    <comment ref="B9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1524,7 +1517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000005000000}">
+    <comment ref="O9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1548,7 +1541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000006000000}">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1572,7 +1565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000007000000}">
+    <comment ref="H10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1596,7 +1589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000008000000}">
+    <comment ref="E11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1620,7 +1613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000009000000}">
+    <comment ref="K11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1644,7 +1637,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000A000000}">
+    <comment ref="E12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1668,7 +1661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000B000000}">
+    <comment ref="K12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1692,7 +1685,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000C000000}">
+    <comment ref="A13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1721,12 +1714,12 @@
 </file>
 
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Geoffrey Nyaga</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1750,7 +1743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
+    <comment ref="A5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1774,7 +1767,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
+    <comment ref="A6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -7133,7 +7126,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="11">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -7147,7 +7140,7 @@
     <numFmt numFmtId="171" formatCode="0.000"/>
     <numFmt numFmtId="172" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="101">
+  <fonts count="101" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8781,7 +8774,7 @@
     <cellStyle name="Title" xfId="6" builtinId="15"/>
     <cellStyle name="Total" xfId="8" builtinId="25"/>
   </cellStyles>
-  <dxfs count="159">
+  <dxfs count="158">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -9131,24 +9124,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -14999,6 +14974,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -15874,6 +15850,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -15996,6 +15973,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -16201,6 +16179,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -28559,132 +28538,132 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table28" displayName="Table28" ref="I15:L29" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="Table28" displayName="Table28" ref="I15:L29" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" headerRowDxfId="158" dataDxfId="157"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" headerRowDxfId="156" dataDxfId="155"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column4" headerRowDxfId="154" dataDxfId="153" headerRowCellStyle="Currency" dataCellStyle="Currency"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="157" dataDxfId="156"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="155" dataDxfId="154"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="153" dataDxfId="152" headerRowCellStyle="Currency" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Table9" displayName="Table9" ref="G32:J37" totalsRowShown="0">
-  <autoFilter ref="G32:J37" xr:uid="{00000000-0009-0000-0100-000009000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="G32:J37" totalsRowShown="0">
+  <autoFilter ref="G32:J37">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="MTOW ="/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="."/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="5850" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="lbs"/>
+    <tableColumn id="1" name="MTOW ="/>
+    <tableColumn id="2" name="."/>
+    <tableColumn id="3" name="5850" dataDxfId="118"/>
+    <tableColumn id="4" name="lbs"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Table1" displayName="Table1" ref="A10:C11" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A10:C11" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Column2" headerRowDxfId="118" dataDxfId="117"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="117" dataDxfId="116"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Table2" displayName="Table2" ref="A14:C18" totalsRowShown="0">
-  <autoFilter ref="A14:C18" xr:uid="{00000000-0009-0000-0100-000002000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A14:C18" totalsRowShown="0">
+  <autoFilter ref="A14:C18">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name=" Vmax   " dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="170"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="knots"/>
+    <tableColumn id="1" name=" Vmax   " dataDxfId="115"/>
+    <tableColumn id="2" name="170"/>
+    <tableColumn id="3" name="knots"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="Table3" displayName="Table3" ref="A21:C30" totalsRowShown="0">
-  <autoFilter ref="A21:C30" xr:uid="{00000000-0009-0000-0100-000003000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A21:C30" totalsRowShown="0">
+  <autoFilter ref="A21:C30">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="STO" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="1500"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="ft"/>
+    <tableColumn id="1" name="STO" dataDxfId="114"/>
+    <tableColumn id="2" name="1500"/>
+    <tableColumn id="3" name="ft"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Table4" displayName="Table4" ref="F11:H12" totalsRowShown="0" headerRowDxfId="114">
-  <autoFilter ref="F11:H12" xr:uid="{00000000-0009-0000-0100-000004000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="F11:H12" totalsRowShown="0" headerRowDxfId="113">
+  <autoFilter ref="F11:H12">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="ROC" dataDxfId="113"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="1600" dataDxfId="112"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="fpm"/>
+    <tableColumn id="1" name="ROC" dataDxfId="112"/>
+    <tableColumn id="2" name="1600" dataDxfId="111"/>
+    <tableColumn id="3" name="fpm"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Table5" displayName="Table5" ref="F15:H18" totalsRowShown="0">
-  <autoFilter ref="F15:H18" xr:uid="{00000000-0009-0000-0100-000005000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="F15:H18" totalsRowShown="0">
+  <autoFilter ref="F15:H18">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="ceiling" dataDxfId="111"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="18000"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="ft"/>
+    <tableColumn id="1" name="ceiling" dataDxfId="110"/>
+    <tableColumn id="2" name="18000"/>
+    <tableColumn id="3" name="ft"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Table11" displayName="Table11" ref="J3:P21" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table11" displayName="Table11" ref="J3:P21" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="Column1">
+    <tableColumn id="1" name="Column1">
       <calculatedColumnFormula>J3+1.5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="Column2">
+    <tableColumn id="2" name="Column2">
       <calculatedColumnFormula>0.5*$B$2*$B$10*($B$11*1.688)^2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="Column3" headerRowDxfId="110" dataDxfId="109">
+    <tableColumn id="3" name="Column3" headerRowDxfId="109" dataDxfId="108">
       <calculatedColumnFormula>L3+2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="Column4">
+    <tableColumn id="4" name="Column4">
       <calculatedColumnFormula>'MTOW &amp; WEIGHTS'!$B$27*550/((0.5*'Sref and POWER SIZING'!$B$2*('Sref and POWER SIZING'!$B$14*1.688)^3*'Sref and POWER SIZING'!$B$15/'Sref and POWER SIZING'!J3)+(2*'Sref and POWER SIZING'!$B$16*'Sref and POWER SIZING'!J3/('Sref and POWER SIZING'!$B$5*'Sref and POWER SIZING'!$B$6*'Sref and POWER SIZING'!$B$14*1.688)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="Column5">
+    <tableColumn id="5" name="Column5">
       <calculatedColumnFormula>( (1-EXP(0.6*$B$2*32.17*$B$29*$B$21/J3))/( $B$30-($B$30+$B$29/$B$27)*(EXP(0.6*$B$2*32.17*$B$29*$B$21/J3))))*(550*$B$28/($B$23*1.688))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="Column6">
+    <tableColumn id="6" name="Column6">
       <calculatedColumnFormula>1/ ( ($G$11/(60*$G$12*550))+ SQRT(2*J3/($B$2*SQRT(3*$B$15/$B$16)))*(1.155/('MTOW &amp; WEIGHTS'!$B$25*'Sref and POWER SIZING'!$G$12*550)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="Column7">
+    <tableColumn id="7" name="Column7">
       <calculatedColumnFormula>$G$17/( ($G$18/(60*$G$12*550))+((SQRT(2*J3/($G$16*SQRT(3*$B$15/$B$16))))*(1.155/($G$12*550*'MTOW &amp; WEIGHTS'!$B$25))))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -28693,64 +28672,64 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table16" displayName="Table16" ref="D2:H7" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table16" displayName="Table16" ref="D2:H7" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="Column5"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="5" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="Table17" displayName="Table17" ref="A2:C6" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table17" displayName="Table17" ref="A2:C6" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="Column1" dataDxfId="108"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" dataDxfId="107"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{00000000-000C-0000-FFFF-FFFF12000000}" name="Table26" displayName="Table26" ref="A87:H103" headerRowCount="0" totalsRowShown="0" headerRowDxfId="107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="Table26" displayName="Table26" ref="A87:H103" headerRowCount="0" totalsRowShown="0" headerRowDxfId="106">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1200-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1200-000002000000}" name="Column2" headerRowDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1200-000003000000}" name="Column3" headerRowDxfId="105"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1200-000004000000}" name="Column4" headerRowDxfId="104"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1200-000005000000}" name="Column5" headerRowDxfId="103"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1200-000006000000}" name="Column6" headerRowDxfId="102"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1200-000007000000}" name="Column7" headerRowDxfId="101"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1200-000008000000}" name="Column8" headerRowDxfId="100" dataDxfId="99"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="105"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="104"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="103"/>
+    <tableColumn id="5" name="Column5" headerRowDxfId="102"/>
+    <tableColumn id="6" name="Column6" headerRowDxfId="101"/>
+    <tableColumn id="7" name="Column7" headerRowDxfId="100"/>
+    <tableColumn id="8" name="Column8" headerRowDxfId="99" dataDxfId="98"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table29" displayName="Table29" ref="S31:X53" headerRowCount="0" totalsRowShown="0" headerRowDxfId="152">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="Table29" displayName="Table29" ref="S31:X53" headerRowCount="0" totalsRowShown="0" headerRowDxfId="151">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Column1">
+    <tableColumn id="1" name="Column1">
       <calculatedColumnFormula>M30+0.5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Column2" dataDxfId="151">
+    <tableColumn id="2" name="Column2" dataDxfId="150">
       <calculatedColumnFormula>$C$32+($C$33*M31)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Column3" dataDxfId="150">
+    <tableColumn id="3" name="Column3" dataDxfId="149">
       <calculatedColumnFormula>$C$32</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Column4" headerRowDxfId="149" dataDxfId="148">
+    <tableColumn id="4" name="Column4" headerRowDxfId="148" dataDxfId="147">
       <calculatedColumnFormula>$C$34*M31</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Column5" headerRowDxfId="147" dataDxfId="146">
+    <tableColumn id="5" name="Column5" headerRowDxfId="146" dataDxfId="145">
       <calculatedColumnFormula>$C$35*M31</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Column6" headerRowDxfId="145" dataDxfId="144">
+    <tableColumn id="6" name="Column6" headerRowDxfId="144" dataDxfId="143">
       <calculatedColumnFormula>$C$36*M31</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -28759,62 +28738,62 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{00000000-000C-0000-FFFF-FFFF13000000}" name="Table27" displayName="Table27" ref="K94:N103" headerRowCount="0" totalsRowShown="0" headerRowDxfId="98">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="Table27" displayName="Table27" ref="K94:N103" headerRowCount="0" totalsRowShown="0" headerRowDxfId="97">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1300-000001000000}" name="Column1" headerRowDxfId="97"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1300-000002000000}" name="Column2" headerRowDxfId="96" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1300-000003000000}" name="Column3" headerRowDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1300-000004000000}" name="Column4" headerRowDxfId="93"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="96"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="95" dataDxfId="94"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="93"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF14000000}" name="Table15" displayName="Table15" ref="A5:C29" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Table15" displayName="Table15" ref="A5:C29" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1400-000001000000}" name="Column1" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1400-000002000000}" name="Column2" headerRowDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1400-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" dataDxfId="91"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="90"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF15000000}" name="Table20" displayName="Table20" ref="A3:P21" headerRowCount="0" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Table20" displayName="Table20" ref="A3:P21" headerRowCount="0" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1500-000001000000}" name="Column1" dataDxfId="88"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1500-000002000000}" name="Column2" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1500-000003000000}" name="Column3" headerRowDxfId="86" dataDxfId="85"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1500-000004000000}" name="Column4" headerRowDxfId="84" dataDxfId="83"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1500-000005000000}" name="Column5" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1500-000006000000}" name="Column6" dataDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1500-000007000000}" name="Column7" headerRowDxfId="80" dataDxfId="79"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1500-000008000000}" name="Column8" headerRowDxfId="78" dataDxfId="77"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1500-000009000000}" name="Column9" headerRowDxfId="76" dataDxfId="75"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1500-00000A000000}" name="Column10" headerRowDxfId="74" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1500-00000B000000}" name="Column11" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-1500-00000C000000}" name="Column12" headerRowDxfId="70"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-1500-000010000000}" name="Column16" headerRowDxfId="69"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-1500-00000D000000}" name="Column13" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-1500-00000E000000}" name="Column14" dataDxfId="66"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-1500-00000F000000}" name="Column15" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="1" name="Column1" dataDxfId="87"/>
+    <tableColumn id="2" name="Column2" dataDxfId="86"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="5" name="Column5" dataDxfId="81"/>
+    <tableColumn id="6" name="Column6" dataDxfId="80"/>
+    <tableColumn id="7" name="Column7" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="8" name="Column8" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="9" name="Column9" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="10" name="Column10" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="11" name="Column11" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="12" name="Column12" headerRowDxfId="69"/>
+    <tableColumn id="16" name="Column16" headerRowDxfId="68"/>
+    <tableColumn id="13" name="Column13" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="14" name="Column14" dataDxfId="65"/>
+    <tableColumn id="15" name="Column15" headerRowDxfId="64" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{00000000-000C-0000-FFFF-FFFF16000000}" name="Table22" displayName="Table22" ref="K22:O26" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="Table22" displayName="Table22" ref="K22:O26" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1600-000001000000}" name="Column1" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1600-000002000000}" name="Column2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1600-000005000000}" name="Column5" dataDxfId="62" dataCellStyle="Percent">
+    <tableColumn id="1" name="Column1" dataDxfId="62"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="5" name="Column5" dataDxfId="61" dataCellStyle="Percent">
       <calculatedColumnFormula>Table22[[#This Row],[Column2]]/Table9[[#Headers],[5850]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1600-000003000000}" name="Column3" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1600-000004000000}" name="Column4">
+    <tableColumn id="3" name="Column3" dataDxfId="60"/>
+    <tableColumn id="4" name="Column4">
       <calculatedColumnFormula>L22*N22</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -28823,274 +28802,273 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{00000000-000C-0000-FFFF-FFFF17000000}" name="Table23" displayName="Table23" ref="J27:O38" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Table23" displayName="Table23" ref="J27:O38" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1700-000001000000}" name="Column1" headerRowDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1700-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1700-000003000000}" name="Column3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1700-000006000000}" name="Column6" dataDxfId="59">
+    <tableColumn id="1" name="Column1" headerRowDxfId="59"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="6" name="Column6" dataDxfId="58">
       <calculatedColumnFormula>Table23[[#This Row],[Column3]]/Table9[[#Headers],[5850]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1700-000004000000}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1700-000005000000}" name="Column5"/>
+    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="5" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF18000000}" name="Table10" displayName="Table10" ref="H3:P6" headerRowCount="0" totalsRowShown="0" headerRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="H3:P6" headerRowCount="0" totalsRowShown="0" headerRowDxfId="57">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1800-000001000000}" name="Column1" headerRowDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1800-000002000000}" name="Column2" headerRowDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1800-000003000000}" name="Column3" headerRowDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1800-000004000000}" name="Column4" headerRowDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1800-000005000000}" name="Column5" headerRowDxfId="53">
+    <tableColumn id="1" name="Column1" headerRowDxfId="56"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="55"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="54"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="53"/>
+    <tableColumn id="5" name="Column5" headerRowDxfId="52">
       <calculatedColumnFormula>((K4-0)/(0-J4))*57.3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1800-000006000000}" name="Column6" headerRowDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1800-000007000000}" name="Column7" headerRowDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1800-000008000000}" name="Column8" headerRowDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1800-000009000000}" name="Column9" headerRowDxfId="49"/>
+    <tableColumn id="6" name="Column6" headerRowDxfId="51"/>
+    <tableColumn id="7" name="Column7" headerRowDxfId="50"/>
+    <tableColumn id="8" name="Column8" headerRowDxfId="49"/>
+    <tableColumn id="9" name="Column9" headerRowDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF19000000}" name="Table12" displayName="Table12" ref="A4:C17" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table12" displayName="Table12" ref="A4:C17" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1900-000001000000}" name="Column1" headerRowDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1900-000002000000}" name="Column2" headerRowDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1900-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="47"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="46"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF1A000000}" name="Table13" displayName="Table13" ref="A20:C33" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table13" displayName="Table13" ref="A20:C33" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1A00-000001000000}" name="Column1" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1A00-000002000000}" name="Column2" headerRowDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1A00-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="43"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF1B000000}" name="Table14" displayName="Table14" ref="E4:F8" headerRowCount="0" totalsRowShown="0" headerRowDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table14" displayName="Table14" ref="E4:F8" headerRowCount="0" totalsRowShown="0" headerRowDxfId="42">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1B00-000001000000}" name="Column1" headerRowDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1B00-000002000000}" name="Column2" headerRowDxfId="41" dataDxfId="40" dataCellStyle="Comma"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="41"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="40" dataDxfId="39" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF1C000000}" name="Table18" displayName="Table18" ref="E15:F18" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Table18" displayName="Table18" ref="E15:F18" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1C00-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1C00-000002000000}" name="Column2"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table30" displayName="Table30" ref="J57:M63" headerRowCount="0" totalsRowShown="0" headerRowDxfId="143" headerRowBorderDxfId="142" headerRowCellStyle="Heading 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="Table30" displayName="Table30" ref="J57:M63" headerRowCount="0" totalsRowShown="0" headerRowDxfId="142" headerRowBorderDxfId="141" headerRowCellStyle="Heading 2">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Column1" headerRowDxfId="141" headerRowCellStyle="Heading 2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Column2" headerRowDxfId="140" dataDxfId="139" headerRowCellStyle="Heading 2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Column3" headerRowDxfId="138" headerRowCellStyle="Heading 2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Column4" headerRowDxfId="137" headerRowCellStyle="Heading 2"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="140" headerRowCellStyle="Heading 2"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="139" dataDxfId="138" headerRowCellStyle="Heading 2"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="137" headerRowCellStyle="Heading 2"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="136" headerRowCellStyle="Heading 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{00000000-000C-0000-FFFF-FFFF1D000000}" name="Table21" displayName="Table21" ref="I10:N18" headerRowCount="0" totalsRowShown="0" headerRowDxfId="39">
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1D00-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1D00-000002000000}" name="Column2" headerRowDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1D00-000003000000}" name="Column3" headerRowDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1D00-000004000000}" name="Column4" headerRowDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1D00-000005000000}" name="Column5"/>
-    <tableColumn id="6" xr3:uid="{9354BD6D-1930-46B7-8A0C-2934D3CF3026}" name="Column6" headerRowDxfId="35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="Table21" displayName="Table21" ref="I10:M18" headerRowCount="0" totalsRowShown="0" headerRowDxfId="38">
+  <tableColumns count="5">
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="37"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="36"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="35"/>
+    <tableColumn id="5" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{00000000-000C-0000-FFFF-FFFF1E000000}" name="Table19" displayName="Table19" ref="E9:F12" headerRowCount="0" totalsRowShown="0" headerRowDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Table19" displayName="Table19" ref="E9:F12" headerRowCount="0" totalsRowShown="0" headerRowDxfId="34">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1E00-000001000000}" name="Column1" headerRowDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1E00-000002000000}" name="Column2" headerRowDxfId="32"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="33"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{00000000-000C-0000-FFFF-FFFF1F000000}" name="Table25" displayName="Table25" ref="K23:M33" headerRowCount="0" totalsRowShown="0" headerRowDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Table25" displayName="Table25" ref="K23:M33" headerRowCount="0" totalsRowShown="0" headerRowDxfId="31">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1F00-000001000000}" name="Column1" headerRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1F00-000002000000}" name="Column2" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1F00-000003000000}" name="Column3" headerRowDxfId="27"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="30"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{00000000-000C-0000-FFFF-FFFF20000000}" name="Table24" displayName="Table24" ref="A3:E15" headerRowCount="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="Table24" displayName="Table24" ref="A3:E15" headerRowCount="0" headerRowDxfId="26">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-2000-000001000000}" name="Column1" totalsRowLabel="Total" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-2000-000002000000}" name="Column2" headerRowDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-2000-000003000000}" name="Column3" headerRowDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-2000-000004000000}" name="Column4" headerRowDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-2000-000005000000}" name="Column5" totalsRowFunction="count" headerRowDxfId="19"/>
+    <tableColumn id="1" name="Column1" totalsRowLabel="Total" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="22"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="21"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="20"/>
+    <tableColumn id="5" name="Column5" totalsRowFunction="count" headerRowDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{00000000-000C-0000-FFFF-FFFF21000000}" name="Table34" displayName="Table34" ref="G3:I7" headerRowCount="0" totalsRowShown="0" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="34" name="Table34" displayName="Table34" ref="G3:I7" headerRowCount="0" totalsRowShown="0" tableBorderDxfId="18">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-2100-000001000000}" name="Column1" headerRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-2100-000002000000}" name="Column2" headerRowDxfId="16" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-2100-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="17"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="16" dataDxfId="15"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{00000000-000C-0000-FFFF-FFFF22000000}" name="Table35" displayName="Table35" ref="G10:I13" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="35" name="Table35" displayName="Table35" ref="G10:I13" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-2200-000001000000}" name="Column1" headerRowDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-2200-000002000000}" name="Column2" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-2200-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="14"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{00000000-000C-0000-FFFF-FFFF23000000}" name="Table36" displayName="Table36" ref="K3:M13" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="36" name="Table36" displayName="Table36" ref="K3:M13" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-2300-000001000000}" name="Column1" headerRowDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-2300-000002000000}" name="Column2" headerRowDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-2300-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="11"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="10"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{00000000-000C-0000-FFFF-FFFF24000000}" name="Table37" displayName="Table37" ref="O4:Q9" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="37" name="Table37" displayName="Table37" ref="O4:Q9" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-2400-000001000000}" name="Column1" headerRowDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-2400-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-2400-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="9"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{00000000-000C-0000-FFFF-FFFF25000000}" name="Table38" displayName="Table38" ref="F4:I30" headerRowCount="0" totalsRowShown="0" headerRowDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="38" name="Table38" displayName="Table38" ref="F4:I30" headerRowCount="0" totalsRowShown="0" headerRowDxfId="8">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-2500-000001000000}" name="Column1" headerRowDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-2500-000002000000}" name="Column2" headerRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-2500-000003000000}" name="Column3" headerRowDxfId="5" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-2500-000004000000}" name="Column4" headerRowDxfId="3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="7"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="6"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{00000000-000C-0000-FFFF-FFFF26000000}" name="Table39" displayName="Table39" ref="A2:C7" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="39" name="Table39" displayName="Table39" ref="A2:C7" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-2600-000001000000}" name="Column1" headerRowDxfId="2" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-2600-000002000000}" name="Column2" headerRowDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-2600-000003000000}" name="Column3"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="2" dataDxfId="1"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="0"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table31" displayName="Table31" ref="A49:F77" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="Table31" displayName="Table31" ref="A49:F77" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Column4" dataDxfId="136"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Column5" dataDxfId="135"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Column6"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4" dataDxfId="135"/>
+    <tableColumn id="5" name="Column5" dataDxfId="134"/>
+    <tableColumn id="6" name="Column6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table32" displayName="Table32" ref="C16:G24" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="Table32" displayName="Table32" ref="C16:G24" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Column1" headerRowDxfId="134" dataDxfId="133"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Column3" headerRowDxfId="132" dataDxfId="131"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Column4" headerRowDxfId="130" dataDxfId="129" headerRowCellStyle="Currency" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Column5"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="133" dataDxfId="132"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3" headerRowDxfId="131" dataDxfId="130"/>
+    <tableColumn id="4" name="Column4" headerRowDxfId="129" dataDxfId="128" headerRowCellStyle="Currency" dataCellStyle="Comma"/>
+    <tableColumn id="5" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table33" displayName="Table33" ref="A32:C40" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="33" name="Table33" displayName="Table33" ref="A32:C40" headerRowCount="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Column1" totalsRowLabel="Total"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Column2" headerRowDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Column3" totalsRowFunction="sum" headerRowDxfId="127"/>
+    <tableColumn id="1" name="Column1" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Column2" headerRowDxfId="127"/>
+    <tableColumn id="3" name="Column3" totalsRowFunction="sum" headerRowDxfId="126"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table6" displayName="Table6" ref="A7:C16" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A7:C16" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="PAYLOAD" headerRowDxfId="126"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Column1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Column2"/>
+    <tableColumn id="1" name="PAYLOAD" headerRowDxfId="125"/>
+    <tableColumn id="2" name="Column1"/>
+    <tableColumn id="3" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table7" displayName="Table7" ref="A19:C30" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A19:C30" headerRowCount="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Column1" totalsRowLabel="Total" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Column2" dataDxfId="123" totalsRowDxfId="122"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Column3" totalsRowFunction="count"/>
+    <tableColumn id="1" name="Column1" totalsRowLabel="Total" dataDxfId="124" totalsRowDxfId="123"/>
+    <tableColumn id="2" name="Column2" dataDxfId="122" totalsRowDxfId="121"/>
+    <tableColumn id="3" name="Column3" totalsRowFunction="count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table8" displayName="Table8" ref="A33:B35" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A33:B35" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Column1" headerRowDxfId="121" dataDxfId="120"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Column2"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="120" dataDxfId="119"/>
+    <tableColumn id="2" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -29358,9 +29336,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X77"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="26.26953125" customWidth="1"/>
@@ -29387,7 +29365,7 @@
     <col min="24" max="24" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21">
+    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.5">
       <c r="D1" s="255" t="s">
         <v>538</v>
       </c>
@@ -29405,7 +29383,7 @@
       <c r="P1" s="135"/>
       <c r="Q1" s="135"/>
     </row>
-    <row r="2" spans="1:17" ht="21" customHeight="1">
+    <row r="2" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D2" s="255"/>
       <c r="E2" s="255"/>
       <c r="F2" s="255"/>
@@ -29416,7 +29394,7 @@
       <c r="K2" s="255"/>
       <c r="L2" s="255"/>
     </row>
-    <row r="3" spans="1:17" ht="18.5">
+    <row r="3" spans="1:17" ht="18.5" x14ac:dyDescent="0.45">
       <c r="D3" s="258" t="s">
         <v>454</v>
       </c>
@@ -29428,7 +29406,7 @@
       <c r="J3" s="258"/>
       <c r="K3" s="258"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="F4" s="29"/>
       <c r="G4" s="133"/>
       <c r="H4" s="132"/>
@@ -29439,7 +29417,7 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:17" ht="20.5">
+    <row r="5" spans="1:17" ht="20.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="183" t="s">
         <v>596</v>
       </c>
@@ -29464,7 +29442,7 @@
       </c>
       <c r="M5" s="6"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="140" t="s">
         <v>456</v>
       </c>
@@ -29484,7 +29462,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="16.5">
+    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A7" s="140" t="s">
         <v>463</v>
       </c>
@@ -29505,7 +29483,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="16.5">
+    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="140" t="s">
         <v>458</v>
       </c>
@@ -29516,7 +29494,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="18.5">
+    <row r="9" spans="1:17" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="140" t="s">
         <v>459</v>
       </c>
@@ -29540,7 +29518,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="16.5">
+    <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="140" t="s">
         <v>457</v>
       </c>
@@ -29565,7 +29543,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="16.5">
+    <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A11" s="140" t="s">
         <v>462</v>
       </c>
@@ -29577,7 +29555,7 @@
       </c>
       <c r="E11" s="201"/>
     </row>
-    <row r="12" spans="1:17" ht="16.5">
+    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="140" t="s">
         <v>461</v>
       </c>
@@ -29589,7 +29567,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="16.5">
+    <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A13" s="140" t="s">
         <v>460</v>
       </c>
@@ -29600,7 +29578,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="23.5">
+    <row r="14" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F14" s="257" t="s">
         <v>472</v>
       </c>
@@ -29612,7 +29590,7 @@
       <c r="L14" s="100"/>
       <c r="M14" s="100"/>
     </row>
-    <row r="15" spans="1:17" ht="16.5">
+    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="I15" s="145" t="s">
         <v>500</v>
       </c>
@@ -29625,7 +29603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="16.5">
+    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C16" s="190" t="s">
         <v>602</v>
       </c>
@@ -29650,7 +29628,7 @@
         <v>715608.99820884794</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="16.5">
+    <row r="17" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C17" s="187" t="s">
         <v>599</v>
       </c>
@@ -29672,7 +29650,7 @@
         <v>63555.597905461989</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="16.5">
+    <row r="18" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C18" s="188" t="s">
         <v>600</v>
       </c>
@@ -29694,7 +29672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="17" thickBot="1">
+    <row r="19" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C19" s="191" t="s">
         <v>601</v>
       </c>
@@ -29719,7 +29697,7 @@
         <v>779164.59611430997</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="17" thickTop="1">
+    <row r="20" spans="1:24" ht="17" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C20" s="189" t="s">
         <v>603</v>
       </c>
@@ -29744,7 +29722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="16.5">
+    <row r="21" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C21" s="186"/>
       <c r="E21" s="193"/>
       <c r="I21" s="145" t="s">
@@ -29760,7 +29738,7 @@
       </c>
       <c r="N21" s="137"/>
     </row>
-    <row r="22" spans="1:24" ht="16.5">
+    <row r="22" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C22" s="186" t="s">
         <v>604</v>
       </c>
@@ -29786,7 +29764,7 @@
         <v>104854.4755486597</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="16.5">
+    <row r="23" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C23" s="189" t="s">
         <v>605</v>
       </c>
@@ -29812,7 +29790,7 @@
         <v>-7500</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="16.5">
+    <row r="24" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C24" s="185" t="s">
         <v>606</v>
       </c>
@@ -29838,7 +29816,7 @@
         <v>90480</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="16.5">
+    <row r="25" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="I25" s="145" t="s">
         <v>495</v>
       </c>
@@ -29851,7 +29829,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="I26" s="145" t="s">
         <v>496</v>
       </c>
@@ -29864,7 +29842,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="I27" s="145" t="s">
         <v>497</v>
       </c>
@@ -29873,7 +29851,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="I28" s="138" t="s">
         <v>498</v>
       </c>
@@ -29883,7 +29861,7 @@
         <v>988289.07166296965</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="15" thickBot="1">
+    <row r="29" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="I29" s="138" t="s">
         <v>499</v>
       </c>
@@ -29894,7 +29872,7 @@
         <v>1288289.0716629697</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="22" thickTop="1" thickBot="1">
+    <row r="30" spans="1:24" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" s="256" t="s">
         <v>502</v>
       </c>
@@ -29903,7 +29881,7 @@
       <c r="F30" s="256"/>
       <c r="G30" s="256"/>
     </row>
-    <row r="31" spans="1:24" ht="15" thickTop="1">
+    <row r="31" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="S31" t="s">
         <v>506</v>
       </c>
@@ -29926,7 +29904,7 @@
         <v>1300000</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" s="184" t="s">
         <v>503</v>
       </c>
@@ -29958,7 +29936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" s="162" t="s">
         <v>504</v>
       </c>
@@ -29991,7 +29969,7 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" s="163" t="s">
         <v>505</v>
       </c>
@@ -30028,7 +30006,7 @@
         <v>1300000</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C35" s="134">
         <v>1200000</v>
       </c>
@@ -30062,7 +30040,7 @@
         <v>1950000</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C36" s="134">
         <v>1300000</v>
       </c>
@@ -30094,7 +30072,7 @@
         <v>2600000</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="S37">
         <f t="shared" si="5"/>
         <v>2.5</v>
@@ -30120,7 +30098,7 @@
         <v>3250000</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38" s="161" t="s">
         <v>620</v>
       </c>
@@ -30154,7 +30132,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="18.5">
+    <row r="39" spans="1:24" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B39" s="195" t="s">
         <v>616</v>
       </c>
@@ -30191,7 +30169,7 @@
         <v>4550000</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="S40">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -30217,7 +30195,7 @@
         <v>5200000</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="D41" s="7" t="s">
         <v>529</v>
       </c>
@@ -30246,7 +30224,7 @@
         <v>5850000</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="D42" t="s">
         <v>527</v>
       </c>
@@ -30275,7 +30253,7 @@
         <v>6500000</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="D43" t="s">
         <v>528</v>
       </c>
@@ -30304,7 +30282,7 @@
         <v>7150000</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="S44">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -30330,7 +30308,7 @@
         <v>7800000</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="S45">
         <f t="shared" si="5"/>
         <v>6.5</v>
@@ -30356,7 +30334,7 @@
         <v>8450000</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="S46">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -30382,7 +30360,7 @@
         <v>9100000</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="21.5" thickBot="1">
+    <row r="47" spans="1:24" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C47" s="254" t="s">
         <v>530</v>
       </c>
@@ -30414,7 +30392,7 @@
         <v>9750000</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="15" thickTop="1">
+    <row r="48" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="S48">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -30440,7 +30418,7 @@
         <v>10400000</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="S49">
         <f t="shared" si="5"/>
         <v>8.5</v>
@@ -30466,7 +30444,7 @@
         <v>11050000</v>
       </c>
     </row>
-    <row r="50" spans="1:24" ht="16.5">
+    <row r="50" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A50" s="170" t="s">
         <v>665</v>
       </c>
@@ -30501,7 +30479,7 @@
         <v>11700000</v>
       </c>
     </row>
-    <row r="51" spans="1:24" ht="16.5">
+    <row r="51" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A51" s="169" t="s">
         <v>617</v>
       </c>
@@ -30536,7 +30514,7 @@
         <v>12350000</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="16.5">
+    <row r="52" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A52" s="171" t="s">
         <v>569</v>
       </c>
@@ -30571,7 +30549,7 @@
         <v>13000000</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="16.5">
+    <row r="53" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A53" s="172" t="s">
         <v>570</v>
       </c>
@@ -30606,7 +30584,7 @@
         <v>13650000</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="16.5">
+    <row r="54" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A54" s="173" t="s">
         <v>571</v>
       </c>
@@ -30617,7 +30595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="16.5">
+    <row r="55" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A55" s="172" t="s">
         <v>572</v>
       </c>
@@ -30628,7 +30606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="16.5">
+    <row r="56" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A56" s="174" t="s">
         <v>573</v>
       </c>
@@ -30639,7 +30617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="18" thickBot="1">
+    <row r="57" spans="1:24" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A57" s="175" t="s">
         <v>574</v>
       </c>
@@ -30656,7 +30634,7 @@
       <c r="L57" s="157"/>
       <c r="M57" s="157"/>
     </row>
-    <row r="58" spans="1:24" ht="15" thickTop="1">
+    <row r="58" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B58" s="169" t="s">
         <v>531</v>
       </c>
@@ -30676,7 +30654,7 @@
         <v>1288289.0716629697</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="16.5">
+    <row r="59" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B59" s="180" t="s">
         <v>576</v>
       </c>
@@ -30703,7 +30681,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="60" spans="1:24" ht="16.5">
+    <row r="60" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B60" s="179" t="s">
         <v>577</v>
       </c>
@@ -30730,7 +30708,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="61" spans="1:24" ht="16.5">
+    <row r="61" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C61" s="168" t="s">
         <v>578</v>
       </c>
@@ -30744,7 +30722,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="62" spans="1:24" ht="16.5">
+    <row r="62" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B62" s="161"/>
       <c r="C62" s="168" t="s">
         <v>579</v>
@@ -30769,7 +30747,7 @@
         <v>26742.762183809518</v>
       </c>
     </row>
-    <row r="63" spans="1:24" ht="16.5">
+    <row r="63" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C63" s="168" t="s">
         <v>580</v>
       </c>
@@ -30791,7 +30769,7 @@
         <v>320913.14620571421</v>
       </c>
     </row>
-    <row r="64" spans="1:24" ht="16.5">
+    <row r="64" spans="1:24" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B64" s="171" t="s">
         <v>581</v>
       </c>
@@ -30804,7 +30782,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="65" spans="3:14" ht="16.5">
+    <row r="65" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C65" s="168" t="s">
         <v>582</v>
       </c>
@@ -30818,7 +30796,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="66" spans="3:14">
+    <row r="66" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C66" s="168"/>
       <c r="D66" s="140"/>
       <c r="J66" s="203" t="s">
@@ -30829,7 +30807,7 @@
       <c r="M66" s="202"/>
       <c r="N66" s="202"/>
     </row>
-    <row r="67" spans="3:14" ht="16.5">
+    <row r="67" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C67" s="168" t="s">
         <v>583</v>
       </c>
@@ -30851,7 +30829,7 @@
       <c r="M67" s="202"/>
       <c r="N67" s="202"/>
     </row>
-    <row r="68" spans="3:14" ht="16.5">
+    <row r="68" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C68" s="168" t="s">
         <v>584</v>
       </c>
@@ -30873,7 +30851,7 @@
       <c r="M68" s="202"/>
       <c r="N68" s="202"/>
     </row>
-    <row r="69" spans="3:14" ht="16.5">
+    <row r="69" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C69" s="168" t="s">
         <v>585</v>
       </c>
@@ -30893,7 +30871,7 @@
       <c r="K69" s="182"/>
       <c r="L69" s="182"/>
     </row>
-    <row r="70" spans="3:14" ht="16.5">
+    <row r="70" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C70" s="168" t="s">
         <v>586</v>
       </c>
@@ -30908,7 +30886,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="71" spans="3:14" ht="16.5">
+    <row r="71" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C71" s="168" t="s">
         <v>587</v>
       </c>
@@ -30922,7 +30900,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="72" spans="3:14" ht="16.5">
+    <row r="72" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C72" s="168" t="s">
         <v>588</v>
       </c>
@@ -30937,7 +30915,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="73" spans="3:14" ht="16.5">
+    <row r="73" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C73" s="168" t="s">
         <v>589</v>
       </c>
@@ -30952,7 +30930,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="74" spans="3:14" ht="16.5">
+    <row r="74" spans="3:14" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C74" s="168" t="s">
         <v>590</v>
       </c>
@@ -30967,7 +30945,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="76" spans="3:14" ht="21" thickBot="1">
+    <row r="76" spans="3:14" ht="21" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C76" s="196" t="s">
         <v>591</v>
       </c>
@@ -30979,7 +30957,7 @@
         <v>537057.51417845697</v>
       </c>
     </row>
-    <row r="77" spans="3:14" ht="21" thickTop="1">
+    <row r="77" spans="3:14" ht="21" thickTop="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C77" s="196" t="s">
         <v>592</v>
       </c>
@@ -31020,10 +30998,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:W105"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
@@ -31032,7 +31010,7 @@
     <col min="9" max="9" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="Q1" t="s">
         <v>673</v>
       </c>
@@ -31046,7 +31024,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="16.5">
+    <row r="2" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
       <c r="G2" s="108" t="s">
         <v>79</v>
       </c>
@@ -31063,7 +31041,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="16.5">
+    <row r="3" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
       <c r="O3" s="12" t="s">
         <v>69</v>
       </c>
@@ -31086,7 +31064,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.5">
+    <row r="4" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C4" s="206" t="s">
         <v>323</v>
       </c>
@@ -31126,7 +31104,7 @@
         <v>7465.3182243348811</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B5" s="23"/>
       <c r="O5" s="10">
         <f>O4+250</f>
@@ -31165,7 +31143,7 @@
         <v>7198.6450096483404</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="18.5">
+    <row r="6" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B6" s="16" t="s">
         <v>53</v>
       </c>
@@ -31206,7 +31184,7 @@
         <v>6973.3005567275168</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="98" t="s">
         <v>642</v>
       </c>
@@ -31250,7 +31228,7 @@
         <v>6779.6922092511904</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="98" t="s">
         <v>643</v>
       </c>
@@ -31297,7 +31275,7 @@
         <v>6611.0554881403214</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="73" t="s">
         <v>51</v>
       </c>
@@ -31345,7 +31323,7 @@
         <v>6462.4713111747305</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="98" t="s">
         <v>320</v>
       </c>
@@ -31392,7 +31370,7 @@
         <v>6330.2690112097207</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="73" t="s">
         <v>51</v>
       </c>
@@ -31440,7 +31418,7 @@
         <v>6211.648627412219</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="16.5">
+    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="140" t="s">
         <v>321</v>
       </c>
@@ -31488,7 +31466,7 @@
         <v>6104.4335277250202</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="9"/>
       <c r="B13" s="13" t="s">
         <v>54</v>
@@ -31531,7 +31509,7 @@
         <v>6006.9035076533855</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="98" t="s">
         <v>55</v>
       </c>
@@ -31575,7 +31553,7 @@
         <v>5917.6792421349646</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="98" t="s">
         <v>56</v>
       </c>
@@ -31622,7 +31600,7 @@
         <v>5835.6404592159543</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="16.5">
+    <row r="16" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="70" t="s">
         <v>322</v>
       </c>
@@ -31670,7 +31648,7 @@
         <v>5759.86682298713</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="O17" s="10">
         <f t="shared" si="8"/>
         <v>5750</v>
@@ -31708,7 +31686,7 @@
         <v>5689.5944552735155</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.5">
+    <row r="18" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
         <v>78</v>
       </c>
@@ -31751,7 +31729,7 @@
         <v>5624.1834440550174</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" s="219" t="s">
         <v>57</v>
       </c>
@@ -31795,7 +31773,7 @@
         <v>5563.0932100631198</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" s="219" t="s">
         <v>58</v>
       </c>
@@ -31839,7 +31817,7 @@
         <v>5505.86358566328</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21" s="219" t="s">
         <v>59</v>
       </c>
@@ -31883,7 +31861,7 @@
         <v>5452.1001076479033</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" s="219" t="s">
         <v>60</v>
       </c>
@@ -31927,7 +31905,7 @@
         <v>5401.4624605775898</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" s="253" t="s">
         <v>61</v>
       </c>
@@ -31936,7 +31914,7 @@
         <v>0.9123520949463898</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24" s="219" t="s">
         <v>62</v>
       </c>
@@ -31947,7 +31925,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25" s="219" t="s">
         <v>64</v>
       </c>
@@ -31956,7 +31934,7 @@
         <v>13.547933564579795</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26" s="219" t="s">
         <v>65</v>
       </c>
@@ -31964,7 +31942,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27" s="219" t="s">
         <v>50</v>
       </c>
@@ -31972,7 +31950,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28" s="219" t="s">
         <v>71</v>
       </c>
@@ -31981,7 +31959,7 @@
         <v>0.8560332551941533</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29" s="219" t="s">
         <v>72</v>
       </c>
@@ -31992,7 +31970,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="16.5">
+    <row r="30" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A30" s="102" t="s">
         <v>325</v>
       </c>
@@ -32001,7 +31979,7 @@
         <v>0.1439667448058467</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="26">
+    <row r="32" spans="1:23" ht="26" x14ac:dyDescent="0.6">
       <c r="A32" s="260"/>
       <c r="B32" s="260"/>
       <c r="G32" s="217" t="s">
@@ -32026,7 +32004,7 @@
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:19" ht="15.5">
+    <row r="33" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="212" t="s">
         <v>634</v>
       </c>
@@ -32035,7 +32013,7 @@
       </c>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:19" ht="17.5">
+    <row r="34" spans="1:19" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A34" s="102" t="s">
         <v>635</v>
       </c>
@@ -32054,7 +32032,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="17.5">
+    <row r="35" spans="1:19" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A35" s="102" t="s">
         <v>636</v>
       </c>
@@ -32087,7 +32065,7 @@
       <c r="Q35" s="211"/>
       <c r="R35" s="211"/>
     </row>
-    <row r="36" spans="1:19" ht="17.5">
+    <row r="36" spans="1:19" ht="17.5" x14ac:dyDescent="0.35">
       <c r="G36" s="165" t="s">
         <v>82</v>
       </c>
@@ -32108,7 +32086,7 @@
       <c r="R36" s="211"/>
       <c r="S36" s="211"/>
     </row>
-    <row r="37" spans="1:19" ht="17.5">
+    <row r="37" spans="1:19" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>97</v>
       </c>
@@ -32135,7 +32113,7 @@
       <c r="R37" s="211"/>
       <c r="S37" s="211"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="M38" s="210" t="s">
         <v>678</v>
       </c>
@@ -32144,12 +32122,12 @@
       <c r="P38" s="211"/>
       <c r="Q38" s="211"/>
     </row>
-    <row r="41" spans="1:19" ht="15.5">
+    <row r="41" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="206" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="98" t="s">
         <v>66</v>
       </c>
@@ -32164,7 +32142,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="98" t="s">
         <v>67</v>
       </c>
@@ -32172,7 +32150,7 @@
         <v>1.0296000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="98" t="s">
         <v>85</v>
       </c>
@@ -32181,7 +32159,7 @@
         <v>0.8560332551941533</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="98" t="s">
         <v>86</v>
       </c>
@@ -32190,7 +32168,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="16.5">
+    <row r="48" spans="1:19" ht="16.5" x14ac:dyDescent="0.45">
       <c r="L48" s="5" t="s">
         <v>99</v>
       </c>
@@ -32201,7 +32179,7 @@
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="L49" s="5" t="s">
         <v>98</v>
       </c>
@@ -32209,12 +32187,12 @@
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N51" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N52" s="11">
         <v>2000</v>
       </c>
@@ -32223,7 +32201,7 @@
         <v>0.53490679990990708</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N53" s="11">
         <f t="shared" ref="N53:N64" si="10">N52+500</f>
         <v>2500</v>
@@ -32233,7 +32211,7 @@
         <v>0.30183193304756006</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N54" s="11">
         <f t="shared" si="10"/>
         <v>3000</v>
@@ -32243,7 +32221,7 @@
         <v>0.19322297377106779</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N55" s="11">
         <f t="shared" si="10"/>
         <v>3500</v>
@@ -32253,7 +32231,7 @@
         <v>0.12832446711095136</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N56" s="11">
         <f t="shared" si="10"/>
         <v>4000</v>
@@ -32263,7 +32241,7 @@
         <v>8.4623832918829578E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N57" s="11">
         <f t="shared" si="10"/>
         <v>4500</v>
@@ -32273,7 +32251,7 @@
         <v>5.2979859843008459E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N58" s="11">
         <f t="shared" si="10"/>
         <v>5000</v>
@@ -32283,7 +32261,7 @@
         <v>2.8902941013055905E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N59" s="11">
         <f t="shared" si="10"/>
         <v>5500</v>
@@ -32293,7 +32271,7 @@
         <v>9.9088241118256981E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N60" s="11">
         <f t="shared" si="10"/>
         <v>6000</v>
@@ -32303,7 +32281,7 @@
         <v>-5.4961032483200611E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N61" s="11">
         <f t="shared" si="10"/>
         <v>6500</v>
@@ -32313,7 +32291,7 @@
         <v>-1.8266943690001369E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N62" s="11">
         <f t="shared" si="10"/>
         <v>7000</v>
@@ -32323,7 +32301,7 @@
         <v>-2.9044357032208534E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="210" t="s">
         <v>89</v>
       </c>
@@ -32343,7 +32321,7 @@
         <v>-3.8274857099794612E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N64" s="11">
         <f t="shared" si="10"/>
         <v>8000</v>
@@ -32353,7 +32331,7 @@
         <v>-4.6279580278134169E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C65" s="2" t="s">
         <v>90</v>
       </c>
@@ -32364,7 +32342,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B66" s="210" t="s">
         <v>91</v>
       </c>
@@ -32378,7 +32356,7 @@
       <c r="J66" s="211"/>
       <c r="K66" s="211"/>
     </row>
-    <row r="70" spans="1:11" ht="20" thickBot="1">
+    <row r="70" spans="1:11" ht="20" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C70" s="261" t="s">
         <v>633</v>
       </c>
@@ -32388,12 +32366,12 @@
       <c r="G70" s="261"/>
       <c r="H70" s="261"/>
     </row>
-    <row r="71" spans="1:11" ht="15" thickTop="1">
+    <row r="71" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="I71" s="198" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15" thickBot="1">
+    <row r="72" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="176" t="s">
         <v>627</v>
       </c>
@@ -32405,10 +32383,10 @@
       <c r="G72" s="259"/>
       <c r="H72" s="259"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="176"/>
     </row>
-    <row r="74" spans="1:11" ht="16.5">
+    <row r="74" spans="1:11" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A74" s="176"/>
       <c r="B74" s="20" t="s">
         <v>93</v>
@@ -32424,7 +32402,7 @@
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="176"/>
       <c r="D75" s="215" t="s">
         <v>95</v>
@@ -32441,10 +32419,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="176"/>
     </row>
-    <row r="77" spans="1:11" ht="15" thickBot="1">
+    <row r="77" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="176" t="s">
         <v>628</v>
       </c>
@@ -32456,10 +32434,10 @@
       <c r="G77" s="259"/>
       <c r="H77" s="259"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="176"/>
     </row>
-    <row r="79" spans="1:11" ht="16.5">
+    <row r="79" spans="1:11" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A79" s="176"/>
       <c r="B79" s="20" t="s">
         <v>100</v>
@@ -32476,7 +32454,7 @@
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:11" ht="15">
+    <row r="80" spans="1:11" ht="15" x14ac:dyDescent="0.4">
       <c r="A80" s="176"/>
       <c r="D80" s="216" t="s">
         <v>638</v>
@@ -32493,13 +32471,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="176"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="176"/>
     </row>
-    <row r="83" spans="1:10" ht="15" thickBot="1">
+    <row r="83" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="176" t="s">
         <v>629</v>
       </c>
@@ -32510,7 +32488,7 @@
       <c r="F83" s="259"/>
       <c r="G83" s="259"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="176"/>
       <c r="B84" t="s">
         <v>102</v>
@@ -32523,7 +32501,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="16.5">
+    <row r="85" spans="1:10" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A85" s="176"/>
       <c r="B85" s="20" t="s">
         <v>103</v>
@@ -32544,7 +32522,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="23"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="176"/>
       <c r="E86" s="216" t="s">
         <v>107</v>
@@ -32558,10 +32536,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="176"/>
     </row>
-    <row r="88" spans="1:10" ht="15" thickBot="1">
+    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="176" t="s">
         <v>630</v>
       </c>
@@ -32574,7 +32552,7 @@
       <c r="G88" s="259"/>
       <c r="H88" s="259"/>
     </row>
-    <row r="89" spans="1:10" ht="16.5">
+    <row r="89" spans="1:10" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A89" s="176"/>
       <c r="B89" t="s">
         <v>108</v>
@@ -32590,7 +32568,7 @@
       <c r="F89" s="213"/>
       <c r="G89" s="213"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="176"/>
       <c r="B90" t="s">
         <v>110</v>
@@ -32600,7 +32578,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="176"/>
       <c r="B91" s="22" t="s">
         <v>111</v>
@@ -32619,7 +32597,7 @@
         <v>-4.9999999999999989E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="176"/>
       <c r="C92" s="194">
         <f>(C91-C90)*C89</f>
@@ -32641,13 +32619,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="176"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="176"/>
     </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1">
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="176" t="s">
         <v>631</v>
       </c>
@@ -32659,7 +32637,7 @@
       <c r="F95" s="259"/>
       <c r="G95" s="259"/>
     </row>
-    <row r="96" spans="1:10" ht="16.5">
+    <row r="96" spans="1:10" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A96" s="176"/>
       <c r="B96" t="s">
         <v>114</v>
@@ -32674,7 +32652,7 @@
       <c r="E96" s="213"/>
       <c r="F96" s="213"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="176"/>
       <c r="B97" t="s">
         <v>115</v>
@@ -32684,7 +32662,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="176"/>
       <c r="B98" t="s">
         <v>116</v>
@@ -32703,7 +32681,7 @@
         <v>-0.10000000000000009</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="176"/>
       <c r="C99" s="194">
         <f>(-C97+C98)*C96</f>
@@ -32722,10 +32700,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="176"/>
     </row>
-    <row r="101" spans="1:9" ht="15" thickBot="1">
+    <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="176" t="s">
         <v>632</v>
       </c>
@@ -32737,7 +32715,7 @@
       <c r="F101" s="259"/>
       <c r="G101" s="259"/>
     </row>
-    <row r="102" spans="1:9" ht="16.5">
+    <row r="102" spans="1:9" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
         <v>118</v>
       </c>
@@ -32752,7 +32730,7 @@
       <c r="F102" s="213"/>
       <c r="G102" s="213"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>119</v>
       </c>
@@ -32761,7 +32739,7 @@
         <v>13.547933564579795</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>120</v>
       </c>
@@ -32779,7 +32757,7 @@
         <v>-0.34843356457979446</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C105" s="194">
         <f>(-C103+C104)*C102</f>
         <v>42.115274436787736</v>
@@ -32825,10 +32803,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:S104"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.54296875" customWidth="1"/>
     <col min="2" max="5" width="11" customWidth="1"/>
@@ -32840,7 +32818,7 @@
     <col min="15" max="16" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="K1" s="264" t="s">
         <v>42</v>
       </c>
@@ -32859,7 +32837,7 @@
       </c>
       <c r="Q1" s="264"/>
     </row>
-    <row r="2" spans="1:17" ht="17.5">
+    <row r="2" spans="1:17" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A2" s="41" t="s">
         <v>662</v>
       </c>
@@ -32901,7 +32879,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="16.5">
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="41" t="s">
         <v>663</v>
       </c>
@@ -32948,7 +32926,7 @@
         <v>19.614367928784159</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="41" t="s">
         <v>47</v>
       </c>
@@ -32997,7 +32975,7 @@
         <v>18.140884424406934</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17.5">
+    <row r="5" spans="1:17" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
         <v>664</v>
       </c>
@@ -33044,7 +33022,7 @@
         <v>16.968649144764299</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="16.5">
+    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A6" s="221" t="s">
         <v>7</v>
       </c>
@@ -33088,7 +33066,7 @@
         <v>16.005964663954312</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15" thickBot="1">
+    <row r="7" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F7" s="41" t="s">
         <v>40</v>
       </c>
@@ -33125,7 +33103,7 @@
         <v>15.196234591244123</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="20" thickBot="1">
+    <row r="8" spans="1:17" ht="20" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="268" t="s">
         <v>131</v>
       </c>
@@ -33161,7 +33139,7 @@
         <v>14.50232001975658</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.5">
+    <row r="9" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="265" t="s">
         <v>656</v>
       </c>
@@ -33196,7 +33174,7 @@
         <v>13.898672845219135</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="16.5">
+    <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="41" t="s">
         <v>647</v>
       </c>
@@ -33237,7 +33215,7 @@
         <v>13.367046651179882</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15">
+    <row r="11" spans="1:17" ht="15" x14ac:dyDescent="0.4">
       <c r="A11" s="222" t="s">
         <v>48</v>
       </c>
@@ -33285,7 +33263,7 @@
         <v>12.894005397703371</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="16.5">
+    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="F12" s="41" t="s">
         <v>646</v>
       </c>
@@ -33321,7 +33299,7 @@
         <v>12.469400646682477</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.5">
+    <row r="13" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="265" t="s">
         <v>657</v>
       </c>
@@ -33356,7 +33334,7 @@
         <v>12.085400830020811</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>132</v>
       </c>
@@ -33400,7 +33378,7 @@
         <v>11.735850207133192</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15">
+    <row r="15" spans="1:17" ht="15" x14ac:dyDescent="0.4">
       <c r="A15" s="41" t="s">
         <v>49</v>
       </c>
@@ -33446,7 +33424,7 @@
         <v>11.415832620154129</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="16.5">
+    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="41" t="s">
         <v>3</v>
       </c>
@@ -33490,7 +33468,7 @@
         <v>11.121366818975361</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="41" t="s">
         <v>0</v>
       </c>
@@ -33533,7 +33511,7 @@
         <v>10.849188808898075</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="41" t="s">
         <v>2</v>
       </c>
@@ -33579,7 +33557,7 @@
         <v>10.596593240646582</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="J19">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -33609,7 +33587,7 @@
         <v>10.361315768674528</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.5">
+    <row r="20" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="265" t="s">
         <v>328</v>
       </c>
@@ -33644,7 +33622,7 @@
         <v>10.14144440971473</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.5">
+    <row r="21" spans="1:16" ht="17.5" x14ac:dyDescent="0.5">
       <c r="A21" s="224" t="s">
         <v>234</v>
       </c>
@@ -33683,7 +33661,7 @@
         <v>9.9353517998216496</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="16.5">
+    <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A22" s="225" t="s">
         <v>648</v>
       </c>
@@ -33692,7 +33670,7 @@
         <v>1.4869053204776603</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16.5">
+    <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A23" s="41" t="s">
         <v>649</v>
       </c>
@@ -33704,7 +33682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16.5">
+    <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24" s="41" t="s">
         <v>650</v>
       </c>
@@ -33712,7 +33690,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16.5">
+    <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A25" s="41" t="s">
         <v>651</v>
       </c>
@@ -33721,7 +33699,7 @@
         <v>3.0219944010805921E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16.5">
+    <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A26" s="41" t="s">
         <v>652</v>
       </c>
@@ -33730,7 +33708,7 @@
         <v>0.14962326466758191</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16.5">
+    <row r="27" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A27" s="41" t="s">
         <v>653</v>
       </c>
@@ -33739,7 +33717,7 @@
         <v>1.4869053204776599</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16.5">
+    <row r="28" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A28" s="221" t="s">
         <v>654</v>
       </c>
@@ -33748,7 +33726,7 @@
         <v>0.58301407661284199</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16.5">
+    <row r="29" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A29" s="221" t="s">
         <v>655</v>
       </c>
@@ -33757,7 +33735,7 @@
         <v>9.014705184847549E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="221" t="s">
         <v>126</v>
       </c>
@@ -33765,212 +33743,212 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="24" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="24" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="24" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="24" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="22">
+    <row r="77" spans="1:9" ht="22" x14ac:dyDescent="0.5">
       <c r="B77" s="263" t="s">
         <v>173</v>
       </c>
@@ -33979,7 +33957,7 @@
       <c r="E77" s="263"/>
       <c r="F77" s="263"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>174</v>
       </c>
@@ -33987,7 +33965,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="18.5">
+    <row r="80" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>175</v>
       </c>
@@ -34006,7 +33984,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="15.5">
+    <row r="82" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="F82" s="2" t="s">
         <v>177</v>
       </c>
@@ -34018,7 +33996,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="15" thickBot="1">
+    <row r="84" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D84" s="262" t="s">
         <v>447</v>
       </c>
@@ -34026,13 +34004,13 @@
       <c r="F84" s="262"/>
       <c r="G84" s="262"/>
     </row>
-    <row r="85" spans="1:19" ht="15.5" thickTop="1" thickBot="1">
+    <row r="85" spans="1:19" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D85" s="262"/>
       <c r="E85" s="262"/>
       <c r="F85" s="262"/>
       <c r="G85" s="262"/>
     </row>
-    <row r="86" spans="1:19" ht="17" thickTop="1">
+    <row r="86" spans="1:19" ht="17" thickTop="1" x14ac:dyDescent="0.45">
       <c r="J86" s="97" t="s">
         <v>409</v>
       </c>
@@ -34041,7 +34019,7 @@
       </c>
       <c r="L86"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D87" s="100" t="s">
         <v>440</v>
       </c>
@@ -34062,7 +34040,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="18.5">
+    <row r="88" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A88" s="117" t="s">
         <v>412</v>
       </c>
@@ -34075,7 +34053,7 @@
       <c r="H88" s="115"/>
       <c r="S88" s="7"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>441</v>
       </c>
@@ -34097,7 +34075,7 @@
       <c r="H89" s="7"/>
       <c r="S89" s="114"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" s="97">
         <v>1</v>
       </c>
@@ -34130,7 +34108,7 @@
       <c r="N90" s="76"/>
       <c r="O90" s="76"/>
     </row>
-    <row r="91" spans="1:19" ht="18.5">
+    <row r="91" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A91" s="97">
         <v>2</v>
       </c>
@@ -34162,7 +34140,7 @@
       <c r="N91" s="76"/>
       <c r="O91" s="23"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" s="97">
         <v>3</v>
       </c>
@@ -34187,7 +34165,7 @@
       <c r="H92" s="7"/>
       <c r="L92"/>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" s="97">
         <v>4</v>
       </c>
@@ -34212,7 +34190,7 @@
       <c r="H93" s="7"/>
       <c r="L93"/>
     </row>
-    <row r="94" spans="1:19" ht="15.5">
+    <row r="94" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="97">
         <v>5</v>
       </c>
@@ -34241,7 +34219,7 @@
       <c r="M94" s="99"/>
       <c r="N94" s="99"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" s="97">
         <v>6</v>
       </c>
@@ -34273,7 +34251,7 @@
         <v>IO-540-D</v>
       </c>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C96" s="97"/>
       <c r="D96" s="97"/>
       <c r="E96" s="97"/>
@@ -34288,7 +34266,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="18.5">
+    <row r="97" spans="1:14" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A97" s="117" t="s">
         <v>407</v>
       </c>
@@ -34307,7 +34285,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C98" s="97" t="s">
         <v>418</v>
       </c>
@@ -34326,7 +34304,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="97">
         <v>7</v>
       </c>
@@ -34359,7 +34337,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="97">
         <v>8</v>
       </c>
@@ -34392,7 +34370,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="97">
         <v>9</v>
       </c>
@@ -34418,7 +34396,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="97">
         <v>10</v>
       </c>
@@ -34444,7 +34422,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="17.5">
+    <row r="103" spans="1:14" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A103" s="97">
         <v>11</v>
       </c>
@@ -34480,7 +34458,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H104" s="7"/>
     </row>
   </sheetData>
@@ -34519,19 +34497,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AJ57"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" style="41" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1"/>
-    <row r="2" spans="1:3" ht="12" customHeight="1"/>
-    <row r="3" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:3">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="41" t="s">
         <v>31</v>
       </c>
@@ -34543,7 +34521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5">
+    <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
         <v>658</v>
       </c>
@@ -34552,7 +34530,7 @@
         <v>2.521994401080592E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="41" t="s">
         <v>0</v>
       </c>
@@ -34561,7 +34539,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="221" t="s">
         <v>126</v>
       </c>
@@ -34570,7 +34548,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.5">
+    <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" s="41" t="s">
         <v>659</v>
       </c>
@@ -34582,7 +34560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16.5">
+    <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="41" t="s">
         <v>652</v>
       </c>
@@ -34591,7 +34569,7 @@
         <v>0.14962326466758191</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.5">
+    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A11" s="41" t="s">
         <v>648</v>
       </c>
@@ -34600,7 +34578,7 @@
         <v>1.4869053204776603</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5">
+    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="41" t="s">
         <v>660</v>
       </c>
@@ -34611,7 +34589,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="41" t="s">
         <v>15</v>
       </c>
@@ -34622,7 +34600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="41" t="s">
         <v>2</v>
       </c>
@@ -34631,7 +34609,7 @@
         <v>0.81621491008207958</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="41" t="s">
         <v>3</v>
       </c>
@@ -34640,7 +34618,7 @@
         <v>4.9991330177758135E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="16.5">
+    <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="221" t="s">
         <v>747</v>
       </c>
@@ -34649,7 +34627,7 @@
         <v>2.3779999999999999E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16.5">
+    <row r="17" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" s="221" t="s">
         <v>746</v>
       </c>
@@ -34658,7 +34636,7 @@
         <v>1.756074594414648E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="221" t="s">
         <v>7</v>
       </c>
@@ -34667,7 +34645,7 @@
         <v>0.73846702876982673</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="226" t="s">
         <v>450</v>
       </c>
@@ -34675,7 +34653,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="221" t="s">
         <v>35</v>
       </c>
@@ -34686,7 +34664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="16.5">
+    <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A21" s="221" t="s">
         <v>661</v>
       </c>
@@ -34698,7 +34676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="221" t="s">
         <v>16</v>
       </c>
@@ -34710,7 +34688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="227" t="s">
         <v>22</v>
       </c>
@@ -34721,7 +34699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16.5">
+    <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24" s="221" t="s">
         <v>748</v>
       </c>
@@ -34730,7 +34708,7 @@
         <v>1.0655806140627681E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="16.5">
+    <row r="25" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="221" t="s">
         <v>23</v>
       </c>
@@ -34742,7 +34720,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="16.5">
+    <row r="26" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A26" s="221" t="s">
         <v>749</v>
       </c>
@@ -34751,7 +34729,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16.5">
+    <row r="27" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A27" s="221" t="s">
         <v>750</v>
       </c>
@@ -34760,7 +34738,7 @@
         <v>0.44809950128795967</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16.5">
+    <row r="28" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="221" t="s">
         <v>40</v>
       </c>
@@ -34772,7 +34750,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="221" t="s">
         <v>42</v>
       </c>
@@ -34784,12 +34762,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="3:36" ht="15.5">
+    <row r="34" spans="3:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="D34" s="77" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="35" spans="3:36">
+    <row r="35" spans="3:36" x14ac:dyDescent="0.35">
       <c r="D35" s="76" t="s">
         <v>404</v>
       </c>
@@ -34803,7 +34781,7 @@
       <c r="L35" s="76"/>
       <c r="M35" s="76"/>
     </row>
-    <row r="36" spans="3:36">
+    <row r="36" spans="3:36" x14ac:dyDescent="0.35">
       <c r="D36" s="76" t="s">
         <v>330</v>
       </c>
@@ -34817,7 +34795,7 @@
       <c r="L36" s="76"/>
       <c r="M36" s="76"/>
     </row>
-    <row r="37" spans="3:36">
+    <row r="37" spans="3:36" x14ac:dyDescent="0.35">
       <c r="D37" s="76" t="s">
         <v>331</v>
       </c>
@@ -34832,12 +34810,12 @@
       <c r="M37" s="76"/>
       <c r="N37" s="76"/>
     </row>
-    <row r="38" spans="3:36">
+    <row r="38" spans="3:36" x14ac:dyDescent="0.35">
       <c r="D38" s="76" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="3:36">
+    <row r="41" spans="3:36" x14ac:dyDescent="0.35">
       <c r="L41" s="25" t="s">
         <v>11</v>
       </c>
@@ -34872,7 +34850,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="3:36">
+    <row r="42" spans="3:36" x14ac:dyDescent="0.35">
       <c r="C42" s="23"/>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
@@ -34910,7 +34888,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="3:36" ht="16.5">
+    <row r="43" spans="3:36" ht="16.5" x14ac:dyDescent="0.45">
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
       <c r="E43" s="23"/>
@@ -34996,7 +34974,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="3:36">
+    <row r="44" spans="3:36" x14ac:dyDescent="0.35">
       <c r="C44" s="23"/>
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
@@ -35108,7 +35086,7 @@
         <v>0.56473987995011943</v>
       </c>
     </row>
-    <row r="45" spans="3:36">
+    <row r="45" spans="3:36" x14ac:dyDescent="0.35">
       <c r="J45" s="10">
         <f>J44+2</f>
         <v>8</v>
@@ -35218,7 +35196,7 @@
         <v>0.7529865066001592</v>
       </c>
     </row>
-    <row r="46" spans="3:36">
+    <row r="46" spans="3:36" x14ac:dyDescent="0.35">
       <c r="J46" s="10">
         <f t="shared" ref="J46:J57" si="24">J45+2</f>
         <v>10</v>
@@ -35328,7 +35306,7 @@
         <v>0.94123313325019897</v>
       </c>
     </row>
-    <row r="47" spans="3:36">
+    <row r="47" spans="3:36" x14ac:dyDescent="0.35">
       <c r="J47" s="10">
         <f t="shared" si="24"/>
         <v>12</v>
@@ -35438,7 +35416,7 @@
         <v>1.1294797599002389</v>
       </c>
     </row>
-    <row r="48" spans="3:36">
+    <row r="48" spans="3:36" x14ac:dyDescent="0.35">
       <c r="J48" s="10">
         <f t="shared" si="24"/>
         <v>14</v>
@@ -35548,7 +35526,7 @@
         <v>1.3177263865502786</v>
       </c>
     </row>
-    <row r="49" spans="10:36">
+    <row r="49" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J49" s="10">
         <f t="shared" si="24"/>
         <v>16</v>
@@ -35658,7 +35636,7 @@
         <v>1.5059730132003184</v>
       </c>
     </row>
-    <row r="50" spans="10:36">
+    <row r="50" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J50" s="10">
         <f t="shared" si="24"/>
         <v>18</v>
@@ -35768,7 +35746,7 @@
         <v>1.6942196398503582</v>
       </c>
     </row>
-    <row r="51" spans="10:36">
+    <row r="51" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J51" s="10">
         <f t="shared" si="24"/>
         <v>20</v>
@@ -35878,7 +35856,7 @@
         <v>1.8824662665003979</v>
       </c>
     </row>
-    <row r="52" spans="10:36">
+    <row r="52" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J52" s="10">
         <f t="shared" si="24"/>
         <v>22</v>
@@ -35988,7 +35966,7 @@
         <v>2.0707128931504379</v>
       </c>
     </row>
-    <row r="53" spans="10:36">
+    <row r="53" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J53" s="10">
         <f t="shared" si="24"/>
         <v>24</v>
@@ -36098,7 +36076,7 @@
         <v>2.2589595198004777</v>
       </c>
     </row>
-    <row r="54" spans="10:36">
+    <row r="54" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J54" s="10">
         <f t="shared" si="24"/>
         <v>26</v>
@@ -36208,7 +36186,7 @@
         <v>2.4472061464505175</v>
       </c>
     </row>
-    <row r="55" spans="10:36">
+    <row r="55" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J55" s="10">
         <f t="shared" si="24"/>
         <v>28</v>
@@ -36318,7 +36296,7 @@
         <v>2.6354527731005573</v>
       </c>
     </row>
-    <row r="56" spans="10:36">
+    <row r="56" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J56" s="10">
         <f t="shared" si="24"/>
         <v>30</v>
@@ -36428,7 +36406,7 @@
         <v>2.823699399750597</v>
       </c>
     </row>
-    <row r="57" spans="10:36">
+    <row r="57" spans="10:36" x14ac:dyDescent="0.35">
       <c r="J57" s="10">
         <f t="shared" si="24"/>
         <v>32</v>
@@ -36553,10 +36531,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A3:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -36569,7 +36547,7 @@
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" ht="15.5">
+    <row r="3" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C3" s="47" t="s">
         <v>203</v>
       </c>
@@ -36587,7 +36565,7 @@
       <c r="N3" s="48"/>
       <c r="P3" s="40"/>
     </row>
-    <row r="4" spans="1:20" ht="22.5" customHeight="1">
+    <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E4" s="65" t="s">
         <v>277</v>
       </c>
@@ -36632,7 +36610,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="16.5">
+    <row r="5" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A5" s="40"/>
       <c r="B5" s="40"/>
       <c r="C5" s="40" t="s">
@@ -36664,7 +36642,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="228" t="s">
         <v>751</v>
       </c>
@@ -36723,7 +36701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="16.5">
+    <row r="7" spans="1:20" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="228" t="s">
         <v>752</v>
       </c>
@@ -36777,7 +36755,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="16.5">
+    <row r="8" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="228" t="s">
         <v>753</v>
       </c>
@@ -36828,7 +36806,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="16.5">
+    <row r="9" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" s="228" t="s">
         <v>754</v>
       </c>
@@ -36883,7 +36861,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="16.5">
+    <row r="10" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="228" t="s">
         <v>755</v>
       </c>
@@ -36934,7 +36912,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="228" t="s">
         <v>756</v>
       </c>
@@ -36987,7 +36965,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="228" t="s">
         <v>757</v>
       </c>
@@ -37046,7 +37024,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="16.5">
+    <row r="13" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A13" s="228" t="s">
         <v>758</v>
       </c>
@@ -37108,7 +37086,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="16.5">
+    <row r="14" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="228" t="s">
         <v>759</v>
       </c>
@@ -37161,7 +37139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="16.5">
+    <row r="15" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A15" s="228" t="s">
         <v>760</v>
       </c>
@@ -37207,7 +37185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="16.5">
+    <row r="16" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="228" t="s">
         <v>761</v>
       </c>
@@ -37256,7 +37234,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="228" t="s">
         <v>762</v>
       </c>
@@ -37315,7 +37293,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="16.5">
+    <row r="18" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A18" s="228" t="s">
         <v>763</v>
       </c>
@@ -37368,7 +37346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="16.5">
+    <row r="19" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A19" s="24"/>
       <c r="B19" s="55"/>
       <c r="C19" s="40"/>
@@ -37403,7 +37381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="16.5">
+    <row r="20" spans="1:20" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A20" s="78"/>
       <c r="B20" s="55"/>
       <c r="C20" s="40"/>
@@ -37436,7 +37414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="78"/>
       <c r="B21" s="55"/>
       <c r="C21" s="40"/>
@@ -37459,7 +37437,7 @@
       <c r="O21" s="40"/>
       <c r="P21" s="40"/>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="K22" s="84" t="s">
         <v>283</v>
       </c>
@@ -37480,7 +37458,7 @@
         <v>2893.0439638293142</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="K23" s="84" t="s">
         <v>284</v>
       </c>
@@ -37499,7 +37477,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="K24" s="86" t="s">
         <v>285</v>
       </c>
@@ -37520,7 +37498,7 @@
       </c>
       <c r="R24" s="150"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="K25" s="84" t="s">
         <v>286</v>
       </c>
@@ -37540,7 +37518,7 @@
         <v>1052.8</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="K26" s="84" t="s">
         <v>287</v>
       </c>
@@ -37560,12 +37538,12 @@
         <v>1146.4959999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="J27" s="4" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="15.5">
+    <row r="28" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C28" s="77" t="s">
         <v>522</v>
       </c>
@@ -37590,7 +37568,7 @@
         <v>15052.29124184315</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15.5">
+    <row r="29" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B29" s="77" t="s">
         <v>523</v>
       </c>
@@ -37607,7 +37585,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15.5">
+    <row r="30" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B30" s="77" t="s">
         <v>524</v>
       </c>
@@ -37632,7 +37610,7 @@
         <v>10973.751278013837</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.5">
+    <row r="31" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B31" s="77" t="s">
         <v>525</v>
       </c>
@@ -37649,7 +37627,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.5">
+    <row r="32" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B32" s="77" t="s">
         <v>526</v>
       </c>
@@ -37673,7 +37651,7 @@
         <v>18101.534441843149</v>
       </c>
     </row>
-    <row r="33" spans="10:15">
+    <row r="33" spans="10:15" x14ac:dyDescent="0.35">
       <c r="J33" s="50"/>
       <c r="M33" s="4" t="s">
         <v>220</v>
@@ -37686,7 +37664,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="34" spans="10:15" ht="17.5">
+    <row r="34" spans="10:15" ht="17.5" x14ac:dyDescent="0.35">
       <c r="J34" s="51" t="s">
         <v>246</v>
       </c>
@@ -37708,7 +37686,7 @@
         <v>19154.334441843148</v>
       </c>
     </row>
-    <row r="35" spans="10:15" ht="21">
+    <row r="35" spans="10:15" ht="21" x14ac:dyDescent="0.5">
       <c r="M35" s="4" t="s">
         <v>220</v>
       </c>
@@ -37720,7 +37698,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="36" spans="10:15">
+    <row r="36" spans="10:15" x14ac:dyDescent="0.35">
       <c r="K36" t="s">
         <v>288</v>
       </c>
@@ -37732,7 +37710,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="10:15">
+    <row r="37" spans="10:15" x14ac:dyDescent="0.35">
       <c r="K37" t="s">
         <v>289</v>
       </c>
@@ -37744,7 +37722,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="10:15">
+    <row r="38" spans="10:15" x14ac:dyDescent="0.35">
       <c r="K38" s="4" t="s">
         <v>220</v>
       </c>
@@ -37754,7 +37732,7 @@
       </c>
       <c r="M38" s="63"/>
     </row>
-    <row r="40" spans="10:15">
+    <row r="40" spans="10:15" x14ac:dyDescent="0.35">
       <c r="L40" s="64"/>
     </row>
   </sheetData>
@@ -37774,10 +37752,10 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AI49"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.7265625" customWidth="1"/>
     <col min="4" max="4" width="6.7265625" customWidth="1"/>
@@ -37789,7 +37767,7 @@
     <col min="35" max="35" width="9.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I1" s="267" t="s">
         <v>336</v>
       </c>
@@ -37797,7 +37775,7 @@
       <c r="K1" s="267"/>
       <c r="L1" s="267"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="273" t="s">
         <v>333</v>
       </c>
@@ -37823,7 +37801,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B3" s="71" t="s">
         <v>334</v>
       </c>
@@ -37855,7 +37833,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16.5">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A4" s="273" t="s">
         <v>251</v>
       </c>
@@ -37889,7 +37867,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="273" t="s">
         <v>264</v>
       </c>
@@ -37912,7 +37890,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="273" t="s">
         <v>265</v>
       </c>
@@ -37934,7 +37912,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="274" t="s">
         <v>302</v>
       </c>
@@ -37955,7 +37933,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="273" t="s">
         <v>303</v>
       </c>
@@ -37964,7 +37942,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>304</v>
       </c>
@@ -37976,12 +37954,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
       <c r="X33" s="83" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="16.5">
+    <row r="34" spans="1:35" ht="16.5" x14ac:dyDescent="0.45">
       <c r="G34" s="264" t="s">
         <v>309</v>
       </c>
@@ -38007,7 +37985,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="16.5">
+    <row r="35" spans="1:35" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A35" s="10" t="s">
         <v>307</v>
       </c>
@@ -38108,7 +38086,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>0</v>
       </c>
@@ -38246,7 +38224,7 @@
         <v>-5.1302530817607881</v>
       </c>
     </row>
-    <row r="37" spans="1:35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>0</v>
       </c>
@@ -38387,7 +38365,7 @@
         <v>-4.7549314645101273</v>
       </c>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>0</v>
       </c>
@@ -38527,7 +38505,7 @@
         <v>-4.3796098472594673</v>
       </c>
     </row>
-    <row r="39" spans="1:35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>0</v>
       </c>
@@ -38668,7 +38646,7 @@
         <v>-3.9855221491462736</v>
       </c>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>0</v>
       </c>
@@ -38801,7 +38779,7 @@
         <v>-3.876262591129195</v>
       </c>
     </row>
-    <row r="41" spans="1:35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>0</v>
       </c>
@@ -38930,7 +38908,7 @@
         <v>-3.5842297737529218</v>
       </c>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>0</v>
       </c>
@@ -39054,7 +39032,7 @@
         <v>-2.8987606491313453</v>
       </c>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>10000</v>
       </c>
@@ -39177,7 +39155,7 @@
         <v>-2.8783233782568249</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>10000</v>
       </c>
@@ -39294,7 +39272,7 @@
         <v>-2.5030017610061646</v>
       </c>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>10000</v>
       </c>
@@ -39402,7 +39380,7 @@
         <v>-1.9400193351301738</v>
       </c>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>10000</v>
       </c>
@@ -39510,7 +39488,7 @@
         <v>-1.8461889308175086</v>
       </c>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>10000</v>
       </c>
@@ -39618,7 +39596,7 @@
         <v>-1.7523585265048434</v>
       </c>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>10000</v>
       </c>
@@ -39726,7 +39704,7 @@
         <v>-1.5646977178795134</v>
       </c>
     </row>
-    <row r="49" spans="1:35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>10000</v>
       </c>
@@ -39859,10 +39837,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A2:P33"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
@@ -39871,12 +39849,12 @@
     <col min="8" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="18.5">
+    <row r="2" spans="1:15" ht="18.5" x14ac:dyDescent="0.45">
       <c r="I2" s="45" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="H3" s="28"/>
       <c r="I3" s="28" t="s">
         <v>208</v>
@@ -39897,7 +39875,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4" s="28" t="s">
         <v>180</v>
       </c>
@@ -39927,7 +39905,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>182</v>
       </c>
@@ -39960,7 +39938,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>183</v>
       </c>
@@ -40000,7 +39978,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>185</v>
       </c>
@@ -40019,7 +39997,7 @@
         <v>4143580.8342413362</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="16.5">
+    <row r="8" spans="1:15" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>189</v>
       </c>
@@ -40038,7 +40016,7 @@
         <v>9139780.6370296124</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="16.5">
+    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>188</v>
       </c>
@@ -40054,7 +40032,7 @@
       </c>
       <c r="F9" s="66"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>214</v>
       </c>
@@ -40077,7 +40055,7 @@
       </c>
       <c r="L10" s="34"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>215</v>
       </c>
@@ -40109,7 +40087,7 @@
       </c>
       <c r="O11" s="25"/>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="31" t="s">
         <v>217</v>
       </c>
@@ -40138,7 +40116,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>216</v>
       </c>
@@ -40157,7 +40135,7 @@
         <v>4.876004426805971</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="16.5">
+    <row r="14" spans="1:15" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="31" t="s">
         <v>218</v>
       </c>
@@ -40175,7 +40153,7 @@
         <v>0.33033961893414038</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16.5">
+    <row r="15" spans="1:15" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -40200,7 +40178,7 @@
         <v>-7.1677464485709705E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="16.5">
+    <row r="16" spans="1:15" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>232</v>
       </c>
@@ -40226,7 +40204,7 @@
         <v>1.6032183908045976</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16.5">
+    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>408</v>
       </c>
@@ -40249,7 +40227,7 @@
         <v>1.4428965517241379</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="20.5">
+    <row r="18" spans="1:16" ht="20.5" x14ac:dyDescent="0.55000000000000004">
       <c r="E18" s="39" t="s">
         <v>300</v>
       </c>
@@ -40265,7 +40243,7 @@
         <v>1.4428965517241379</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16.5">
+    <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="28" t="s">
         <v>192</v>
@@ -40288,7 +40266,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>199</v>
       </c>
@@ -40307,7 +40285,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="32"/>
       <c r="B22" s="3">
         <f>L4</f>
@@ -40319,7 +40297,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>198</v>
       </c>
@@ -40335,7 +40313,7 @@
       <c r="L23" s="95"/>
       <c r="M23" s="95"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>197</v>
       </c>
@@ -40353,7 +40331,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16.5">
+    <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>196</v>
       </c>
@@ -40377,7 +40355,7 @@
         <v>0.81621491008207958</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16.5">
+    <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>194</v>
       </c>
@@ -40394,7 +40372,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16.5">
+    <row r="27" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>195</v>
       </c>
@@ -40417,7 +40395,7 @@
         <v>0.67092199654312834</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>222</v>
       </c>
@@ -40428,7 +40406,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16.5">
+    <row r="29" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>228</v>
       </c>
@@ -40453,7 +40431,7 @@
         <v>0.85962195130891961</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16.5">
+    <row r="30" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>230</v>
       </c>
@@ -40473,7 +40451,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16.5">
+    <row r="31" spans="1:16" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>231</v>
       </c>
@@ -40495,7 +40473,7 @@
         <v>0.73603419981838547</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>252</v>
       </c>
@@ -40503,7 +40481,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="18.5">
+    <row r="33" spans="1:13" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>373</v>
       </c>
@@ -40545,10 +40523,10 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" style="93" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -40562,7 +40540,7 @@
     <col min="15" max="17" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20" thickBot="1">
+    <row r="1" spans="1:17" ht="20" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D1" s="275" t="s">
         <v>371</v>
       </c>
@@ -40576,10 +40554,10 @@
       <c r="L1" s="275"/>
       <c r="M1" s="275"/>
     </row>
-    <row r="2" spans="1:17" ht="15" thickTop="1">
+    <row r="2" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="H2"/>
     </row>
-    <row r="3" spans="1:17" ht="16.5">
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B3" s="42" t="s">
         <v>369</v>
       </c>
@@ -40603,7 +40581,7 @@
         <v>0.29099999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="16.5">
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="125" t="s">
         <v>367</v>
       </c>
@@ -40646,7 +40624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="16.5">
+    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="125" t="s">
         <v>372</v>
       </c>
@@ -40692,7 +40670,7 @@
         <v>0.21767003168521115</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="16.5">
+    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="125" t="s">
         <v>375</v>
       </c>
@@ -40738,7 +40716,7 @@
         <v>3.7370000000000002E-7</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="16.5">
+    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="125" t="s">
         <v>379</v>
       </c>
@@ -40771,7 +40749,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="16.5">
+    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="125"/>
       <c r="B8" s="42" t="s">
         <v>389</v>
@@ -40799,7 +40777,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="125" t="s">
         <v>381</v>
       </c>
@@ -40833,7 +40811,7 @@
         <v>6.7597682365176048</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="17.5">
+    <row r="10" spans="1:17" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A10" s="125" t="s">
         <v>391</v>
       </c>
@@ -40846,7 +40824,7 @@
       </c>
       <c r="N10" s="93"/>
     </row>
-    <row r="11" spans="1:17" ht="17.5">
+    <row r="11" spans="1:17" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A11" s="127"/>
       <c r="B11" s="9"/>
       <c r="C11" s="128" t="s">
@@ -40877,7 +40855,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17">
+    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.4">
       <c r="A12" s="126" t="s">
         <v>453</v>
       </c>
@@ -40909,7 +40887,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="125" t="s">
         <v>393</v>
       </c>
@@ -40931,10 +40909,10 @@
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="41"/>
     </row>
-    <row r="15" spans="1:17" ht="22.5">
+    <row r="15" spans="1:17" ht="22.5" x14ac:dyDescent="0.45">
       <c r="A15" s="116"/>
       <c r="B15" s="13" t="s">
         <v>396</v>
@@ -40946,7 +40924,7 @@
         <v>2.521994401080592E-2</v>
       </c>
     </row>
-    <row r="21" spans="6:6">
+    <row r="21" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F21" s="93"/>
     </row>
   </sheetData>
@@ -40966,9 +40944,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:R35"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="235" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
@@ -40976,7 +40954,7 @@
     <col min="9" max="9" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="17.5">
+    <row r="2" spans="1:17" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A2" s="235" t="s">
         <v>679</v>
       </c>
@@ -41004,7 +40982,7 @@
       <c r="O2" s="182"/>
       <c r="P2" s="182"/>
     </row>
-    <row r="3" spans="1:17" ht="16.5">
+    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="235" t="s">
         <v>40</v>
       </c>
@@ -41025,7 +41003,7 @@
       <c r="O3" s="182"/>
       <c r="P3" s="182"/>
     </row>
-    <row r="4" spans="1:17" ht="16.5">
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A4" s="235" t="s">
         <v>680</v>
       </c>
@@ -41043,7 +41021,7 @@
       <c r="H4" s="235"/>
       <c r="I4" s="235"/>
     </row>
-    <row r="5" spans="1:17" ht="16.5">
+    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A5" s="102" t="s">
         <v>681</v>
       </c>
@@ -41067,7 +41045,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="102" t="s">
         <v>682</v>
       </c>
@@ -41091,7 +41069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.5">
+    <row r="7" spans="1:17" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A7" s="102" t="s">
         <v>687</v>
       </c>
@@ -41115,7 +41093,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="16.5">
+    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="G8" s="98" t="s">
         <v>722</v>
       </c>
@@ -41130,7 +41108,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="16.5">
+    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B9" s="250" t="s">
         <v>723</v>
       </c>
@@ -41146,7 +41124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="G10" s="98" t="s">
         <v>724</v>
       </c>
@@ -41161,7 +41139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="18.5">
+    <row r="11" spans="1:17" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A11" s="235" t="s">
         <v>742</v>
       </c>
@@ -41193,7 +41171,7 @@
       <c r="P11" s="182"/>
       <c r="Q11" s="182"/>
     </row>
-    <row r="12" spans="1:17" ht="17.5">
+    <row r="12" spans="1:17" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A12" s="235" t="s">
         <v>743</v>
       </c>
@@ -41209,7 +41187,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.5">
+    <row r="13" spans="1:17" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A13" s="235" t="s">
         <v>741</v>
       </c>
@@ -41238,7 +41216,7 @@
       <c r="O13" s="182"/>
       <c r="P13" s="182"/>
     </row>
-    <row r="14" spans="1:17" ht="16.5">
+    <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="235" t="s">
         <v>745</v>
       </c>
@@ -41259,11 +41237,11 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B15" s="235"/>
       <c r="H15" s="235"/>
     </row>
-    <row r="16" spans="1:17" ht="16.5">
+    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B16" s="235"/>
       <c r="F16" s="246" t="s">
         <v>726</v>
@@ -41279,7 +41257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="6:18">
+    <row r="17" spans="6:18" x14ac:dyDescent="0.35">
       <c r="G17" t="s">
         <v>727</v>
       </c>
@@ -41294,7 +41272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="6:18" ht="18.5">
+    <row r="18" spans="6:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="F18" s="165" t="s">
         <v>739</v>
       </c>
@@ -41316,7 +41294,7 @@
       <c r="P18" s="182"/>
       <c r="Q18" s="182"/>
     </row>
-    <row r="19" spans="6:18" ht="18.5">
+    <row r="19" spans="6:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="H19" s="235" t="s">
         <v>705</v>
       </c>
@@ -41325,7 +41303,7 @@
         <v>9.0621109076472681E-3</v>
       </c>
     </row>
-    <row r="20" spans="6:18" ht="16.5">
+    <row r="20" spans="6:18" ht="16.5" x14ac:dyDescent="0.45">
       <c r="H20" s="235" t="s">
         <v>701</v>
       </c>
@@ -41337,7 +41315,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="21" spans="6:18" ht="16.5">
+    <row r="21" spans="6:18" ht="16.5" x14ac:dyDescent="0.45">
       <c r="H21" s="235" t="s">
         <v>704</v>
       </c>
@@ -41349,7 +41327,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="22" spans="6:18" ht="16.5">
+    <row r="22" spans="6:18" ht="16.5" x14ac:dyDescent="0.45">
       <c r="F22" s="245" t="s">
         <v>728</v>
       </c>
@@ -41364,7 +41342,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="6:18" ht="16.5">
+    <row r="23" spans="6:18" ht="16.5" x14ac:dyDescent="0.45">
       <c r="F23" s="165" t="s">
         <v>729</v>
       </c>
@@ -41379,7 +41357,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="6:18" ht="17.5">
+    <row r="24" spans="6:18" ht="17.5" x14ac:dyDescent="0.45">
       <c r="F24" s="165" t="s">
         <v>730</v>
       </c>
@@ -41394,7 +41372,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="25" spans="6:18" ht="17.5">
+    <row r="25" spans="6:18" ht="17.5" x14ac:dyDescent="0.45">
       <c r="H25" s="235" t="s">
         <v>711</v>
       </c>
@@ -41406,7 +41384,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="26" spans="6:18" ht="16.5">
+    <row r="26" spans="6:18" ht="16.5" x14ac:dyDescent="0.45">
       <c r="F26" s="247" t="s">
         <v>731</v>
       </c>
@@ -41421,7 +41399,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="6:18" ht="20.5">
+    <row r="27" spans="6:18" ht="20.5" x14ac:dyDescent="0.45">
       <c r="F27" s="45" t="s">
         <v>732</v>
       </c>
@@ -41433,7 +41411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="6:18" ht="16.5">
+    <row r="28" spans="6:18" ht="16.5" x14ac:dyDescent="0.45">
       <c r="F28" s="245" t="s">
         <v>733</v>
       </c>
@@ -41448,7 +41426,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="6:18" ht="18.5">
+    <row r="30" spans="6:18" ht="18.5" x14ac:dyDescent="0.45">
       <c r="F30" s="248" t="s">
         <v>734</v>
       </c>
@@ -41473,7 +41451,7 @@
       <c r="Q30" s="182"/>
       <c r="R30" s="182"/>
     </row>
-    <row r="31" spans="6:18">
+    <row r="31" spans="6:18" x14ac:dyDescent="0.35">
       <c r="K31" s="249" t="s">
         <v>717</v>
       </c>
@@ -41485,7 +41463,7 @@
       <c r="Q31" s="182"/>
       <c r="R31" s="182"/>
     </row>
-    <row r="32" spans="6:18">
+    <row r="32" spans="6:18" x14ac:dyDescent="0.35">
       <c r="K32" s="249" t="s">
         <v>718</v>
       </c>
@@ -41495,7 +41473,7 @@
       <c r="O32" s="182"/>
       <c r="P32" s="182"/>
     </row>
-    <row r="33" spans="11:18" ht="15.5">
+    <row r="33" spans="11:18" ht="15.5" x14ac:dyDescent="0.35">
       <c r="K33" t="s">
         <v>737</v>
       </c>
@@ -41504,7 +41482,7 @@
         <v>2.1870571246092645</v>
       </c>
     </row>
-    <row r="34" spans="11:18">
+    <row r="34" spans="11:18" x14ac:dyDescent="0.35">
       <c r="L34" s="249" t="s">
         <v>735</v>
       </c>
@@ -41515,7 +41493,7 @@
       <c r="Q34" s="182"/>
       <c r="R34" s="182"/>
     </row>
-    <row r="35" spans="11:18">
+    <row r="35" spans="11:18" x14ac:dyDescent="0.35">
       <c r="L35" s="182" t="s">
         <v>736</v>
       </c>
